--- a/assets/security-review/code-analyzer-false-positives.xlsx
+++ b/assets/security-review/code-analyzer-false-positives.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Scan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Responses'!$A$1:$K$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Responses'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/donation/domain/DonationDesignations.cls:25</t>
+          <t>base/main/default/classes/donation/domain/DonationDesignations.cls:36</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/donor/domain/Contacts.cls:28</t>
+          <t>base/main/default/classes/donor/domain/Contacts.cls:52</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/recurring/domain/RecurringDonations.cls:41</t>
+          <t>base/main/default/classes/recurring/domain/RecurringDonations.cls:61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Third-party (vendored FFLib)</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ApexSharingViolations</t>
+          <t>AvoidHardcodedCredentialsInVarAssign</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -700,32 +700,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/fflib/fflib_SObjectUnitOfWork.cls:59</t>
+          <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Apex classes should declare a sharing model if DML or SOQL/SOSL is used</t>
+          <t>Hard coded credentials assigned to variable: Email_Signature__c  matched the token: SIGNATURE</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>No sharing keyword on a vendored FFLib class</t>
+          <t>Identifiers named credential / signature that hold no secret</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>The Unit of Work class itself. The inner `SimpleDML` that performs the DML is explicitly declared `without sharing` as a documented local fork.</t>
+          <t>Seeds `Settings__c.Email_Signature__c` with `'The &lt;org name&gt; team'` on first install — an email sign-off.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Access level for the Unit of Work comes from whoever constructs it, not from the class itself; a keyword here would not reach the inner `SimpleDML` class that performs the DML, because inner classes do not inherit the container's declaration. The one place this genuinely matters is already patched and documented as a local fork: `SimpleDML` is declared `without sharing` so that guest writes carrying a lookup to a record the Guest License cannot see do not fail at commit.</t>
+          <t>The one remaining site is the identifier pattern matching a name, not a value: `PostInstallHandler` seeds `Settings__c.Email_Signature__c` with `'The &lt;org name&gt; team'` on first install — *signature* there is the closing line of an outbound email, and the field's API name is packaged and cannot be renamed. The other eight hits this rule used to produce were cleared on 2026-09-25 by renaming the identifiers to say what they hold (`donorEndpoint` / `adminEndpoint` for `'callout:' + &lt;Named Credential name&gt;`, `AWAITING_SETUP_LABEL`, `DEFAULT_EMAIL_CLOSING`, `holderName` / `roleSummary`). No secret material exists anywhere in package source: the only place a Stripe key lives is inside a Named Credential the subscriber builds in Setup, which Apex cannot read back.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>The class header carries the explanation in a `// doc:` comment with the Apex Developer Guide citation. The `SimpleDML` fork is entry 3 of the FFLib fork log in DEPENDENCIES.md.</t>
+          <t>`Payment_Account__c.Stripe_*_Restricted_Key__c` are Text(80) fields whose `&lt;description&gt;` states they hold a Named Credential name, consumed as `'callout:' + name`. `scripts/lint/security-review-scan.py` inventories every `key`/`token`/`secret`-named field on each CI run against a baseline. The Named-Credential-only rule is FP-4 in docs/security/appexchange-security-review-readiness.md.</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AvoidHardcodedCredentialsInVarAssign</t>
+          <t>ProtectSensitiveData</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -757,32 +757,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:151</t>
+          <t>base/main/default/objects/Campaign_Design__c/fields/Theme_Tokens_JSON__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Hard coded credentials assigned to variable: Email_Signature__c  matched the token: SIGNATURE</t>
+          <t>Theme_Tokens_JSON__c is a potential auth token in a custom object: Campaign_Design__c</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Identifiers named credential / signature that hold no secret</t>
+          <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Seeds `Settings__c.Email_Signature__c` with `'The &lt;org name&gt; team'` on first install — an email sign-off.</t>
+          <t>CSS design-token overrides as JSON; *token* means a CSS custom property.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>The one remaining site is the identifier pattern matching a name, not a value: `PostInstallHandler` seeds `Settings__c.Email_Signature__c` with `'The &lt;org name&gt; team'` on first install — *signature* there is the closing line of an outbound email, and the field's API name is packaged and cannot be renamed. The other eight hits this rule used to produce were cleared on 2026-09-25 by renaming the identifiers to say what they hold (`donorEndpoint` / `adminEndpoint` for `'callout:' + &lt;Named Credential name&gt;`, `AWAITING_SETUP_LABEL`, `DEFAULT_EMAIL_CLOSING`, `holderName` / `roleSummary`). No secret material exists anywhere in package source: the only place a Stripe key lives is inside a Named Credential the subscriber builds in Setup, which Apex cannot read back.</t>
+          <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>`Payment_Account__c.Stripe_*_Restricted_Key__c` are Text(80) fields whose `&lt;description&gt;` states they hold a Named Credential name, consumed as `'callout:' + name`. `scripts/lint/security-review-scan.py` inventories every `key`/`token`/`secret`-named field on each CI run against a baseline. The Named-Credential-only rule is FP-4 in docs/security/appexchange-security-review-readiness.md.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Campaign_Design__c/fields/Theme_Tokens_JSON__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Donation_Designation__c/fields/Designation__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Theme_Tokens_JSON__c is a potential auth token in a custom object: Campaign_Design__c</t>
+          <t>Designation__c is a potential auth token in a custom object: Donation_Designation__c</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>CSS design-token overrides as JSON; *token* means a CSS custom property.</t>
+          <t>Lookup to the fund a gift split supports; matches on *sign*.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Working as designed</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -871,32 +871,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Donation_Designation__c/fields/Designation__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Donation_Staging__c/fields/Access_Token__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Designation__c is a potential auth token in a custom object: Donation_Designation__c</t>
+          <t>Access_Token__c is a potential auth token in a custom object: Donation_Staging__c</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Field names that merely contain sign, auth, token or credit</t>
+          <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Lookup to the fund a gift split supports; matches on *sign*.</t>
+          <t>256-bit random capability token scoped to one staging row; properties in FP-16.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
+          <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Donation_Staging__c/fields/Access_Token__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Donation_Staging__c/fields/Idempotency_Key__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Access_Token__c is a potential auth token in a custom object: Donation_Staging__c</t>
+          <t>Idempotency_Key__c is a potential auth token in a custom object: Donation_Staging__c</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>256-bit random capability token scoped to one staging row; properties in FP-16.</t>
+          <t>Client-generated ticket-checkout attempt id; unique index is the double-submit backstop.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Donation_Staging__c/fields/Idempotency_Key__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Guest_Request__c/fields/Idempotency_Key__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Idempotency_Key__c is a potential auth token in a custom object: Donation_Staging__c</t>
+          <t>Idempotency_Key__c is a potential auth token in a custom object: Guest_Request__c</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Client-generated ticket-checkout attempt id; unique index is the double-submit backstop.</t>
+          <t>Client-generated request id so a double-click cannot queue the same work twice.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1042,32 +1042,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Guest_Request__c/fields/Idempotency_Key__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Payment_Account__c/fields/Publishable_Key__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Idempotency_Key__c is a potential auth token in a custom object: Guest_Request__c</t>
+          <t>Publishable_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
+          <t>Fields that hold a Named Credential's name, not a key</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Client-generated request id so a double-click cannot queue the same work twice.</t>
+          <t>Stripe publishable key — designed to be sent to the browser; secret key is never in a field.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
+          <t>`Stripe_Donor_Restricted_Key__c` and `Stripe_Admin_Restricted_Key__c` are Text(80) fields holding the **API name** of a Named Credential the subscriber admin built by hand in Setup, and Apex consumes them as `'callout:' + name`. The key itself is inside the Named Credential and is never readable from Apex, a field, or the UI. The fields are per-Payment-Account rather than org-wide because one org can run several gateway accounts (for example one per legal entity), which a hierarchy setting cannot model. `Publishable_Key__c` holds Stripe's publishable key, which Stripe designs to be embedded in browser-side code and is sent to every donor's browser by construction; it authorises nothing on its own.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+          <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. AGENTS.md Rule 9 makes this the required pattern, and FP-4 in docs/security/appexchange-security-review-readiness.md documents it for the reviewer.</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Payment_Account__c/fields/Publishable_Key__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Payment_Account__c/fields/Stripe_Admin_Restricted_Key__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Publishable_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
+          <t>Stripe_Admin_Restricted_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Stripe publishable key — designed to be sent to the browser; secret key is never in a field.</t>
+          <t>Text(80): API name of the Named Credential holding the back-office restricted key.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Payment_Account__c/fields/Stripe_Admin_Restricted_Key__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Payment_Account__c/fields/Stripe_Donor_Restricted_Key__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Stripe_Admin_Restricted_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
+          <t>Stripe_Donor_Restricted_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Text(80): API name of the Named Credential holding the back-office restricted key.</t>
+          <t>Text(80): API name of the Named Credential holding the charge-only restricted key.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1213,32 +1213,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Payment_Account__c/fields/Stripe_Donor_Restricted_Key__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Portal_Access_Token__c/fields/Code_Hash__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Stripe_Donor_Restricted_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
+          <t>Code_Hash__c is a potential auth token in a custom object: Portal_Access_Token__c</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Fields that hold a Named Credential's name, not a key</t>
+          <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Text(80): API name of the Named Credential holding the charge-only restricted key.</t>
+          <t>SHA-256 of the emailed sign-in code, nulled on redemption; the code itself is never stored.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>`Stripe_Donor_Restricted_Key__c` and `Stripe_Admin_Restricted_Key__c` are Text(80) fields holding the **API name** of a Named Credential the subscriber admin built by hand in Setup, and Apex consumes them as `'callout:' + name`. The key itself is inside the Named Credential and is never readable from Apex, a field, or the UI. The fields are per-Payment-Account rather than org-wide because one org can run several gateway accounts (for example one per legal entity), which a hierarchy setting cannot model. `Publishable_Key__c` holds Stripe's publishable key, which Stripe designs to be embedded in browser-side code and is sent to every donor's browser by construction; it authorises nothing on its own.</t>
+          <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. AGENTS.md Rule 9 makes this the required pattern, and FP-4 in docs/security/appexchange-security-review-readiness.md documents it for the reviewer.</t>
+          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Portal_Access_Token__c/fields/Code_Hash__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Portal_Access_Token__c/fields/Session_Hash__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Code_Hash__c is a potential auth token in a custom object: Portal_Access_Token__c</t>
+          <t>Session_Hash__c is a potential auth token in a custom object: Portal_Access_Token__c</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>SHA-256 of the emailed sign-in code, nulled on redemption; the code itself is never stored.</t>
+          <t>SHA-256 of the browser session token, unique external Id; the token itself is never stored.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Working as designed</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1327,32 +1327,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Portal_Access_Token__c/fields/Session_Hash__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Recurring_Designation__c/fields/Designation__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Session_Hash__c is a potential auth token in a custom object: Portal_Access_Token__c</t>
+          <t>Designation__c is a potential auth token in a custom object: Recurring_Designation__c</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
+          <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>SHA-256 of the browser session token, unique external Id; the token itself is never stored.</t>
+          <t>Lookup to the fund a recurring split supports; matches on *sign*.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
+          <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Recurring_Designation__c/fields/Designation__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Recurring_Donation__c/fields/Designation__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Designation__c is a potential auth token in a custom object: Recurring_Designation__c</t>
+          <t>Designation__c is a potential auth token in a custom object: Recurring_Donation__c</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Lookup to the fund a recurring split supports; matches on *sign*.</t>
+          <t>Single-fund lookup on a recurring schedule; matches on *sign*.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Recurring_Donation__c/fields/Designation__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Recurring_Donation__c/fields/Re_Auth_Link_Sent_At__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Designation__c is a potential auth token in a custom object: Recurring_Donation__c</t>
+          <t>Re_Auth_Link_Sent_At__c is a potential auth token in a custom object: Recurring_Donation__c</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Single-fund lookup on a recurring schedule; matches on *sign*.</t>
+          <t>Timestamp of the last 3-D Secure reminder email; matches on *auth*.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Recurring_Donation__c/fields/Re_Auth_Link_Sent_At__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Recurring_Donation__c/fields/Re_Auth_Required__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Re_Auth_Link_Sent_At__c is a potential auth token in a custom object: Recurring_Donation__c</t>
+          <t>Re_Auth_Required__c is a potential auth token in a custom object: Recurring_Donation__c</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Timestamp of the last 3-D Secure reminder email; matches on *auth*.</t>
+          <t>Checkbox: the donor must complete 3-D Secure on-session; matches on *auth*.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Recurring_Donation__c/fields/Re_Auth_Required__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Settings__c/fields/Default_Designation__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Re_Auth_Required__c is a potential auth token in a custom object: Recurring_Donation__c</t>
+          <t>Default_Designation__c is a potential auth token in the object: Settings__c with public visibility</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Checkbox: the donor must complete 3-D Secure on-session; matches on *auth*.</t>
+          <t>18-character Id of the fallback fund, stored as text because a Custom Setting cannot hold a lookup; matches on *sign*.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Settings__c/fields/Default_Designation__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Settings__c/fields/Email_Signature__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Default_Designation__c is a potential auth token in the object: Settings__c with public visibility</t>
+          <t>Email_Signature__c is a potential auth token in the object: Settings__c with public visibility</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18-character Id of the fallback fund, stored as text because a Custom Setting cannot hold a lookup; matches on *sign*.</t>
+          <t>Sign-off line printed above the footer of every outbound email.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Settings__c/fields/Email_Signature__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Settings__c/fields/Portal_Token_TTL_Hours__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Email_Signature__c is a potential auth token in the object: Settings__c with public visibility</t>
+          <t>Portal_Token_TTL_Hours__c is a potential auth token in the object: Settings__c with public visibility</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Sign-off line printed above the footer of every outbound email.</t>
+          <t>A number of hours — the ceiling on a donor-portal session's lifetime.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Settings__c/fields/Portal_Token_TTL_Hours__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Settings__c/fields/Soft_Credit_Automation_Enabled__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Portal_Token_TTL_Hours__c is a potential auth token in the object: Settings__c with public visibility</t>
+          <t>Soft_Credit_Automation_Enabled__c is a potential auth token in the object: Settings__c with public visibility</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>A number of hours — the ceiling on a donor-portal session's lifetime.</t>
+          <t>Feature toggle for soft-credit rollups; matches on *credit*.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Working as designed</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ProtectSensitiveData</t>
+          <t>LoadJavaScriptHtmlScript</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1778,37 +1778,37 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Settings__c/fields/Soft_Credit_Automation_Enabled__c.field-meta.xml:1</t>
+          <t>base/main/default/pages/stripePayment.page:53</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Soft_Credit_Automation_Enabled__c is a potential auth token in the object: Settings__c with public visibility</t>
+          <t>Javascript should always be loaded from static resources</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Field names that merely contain sign, auth, token or credit</t>
+          <t>Stripe.js loaded from js.stripe.com in the two Visualforce payment pages</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Feature toggle for soft-credit rollups; matches on *credit*.</t>
+          <t>`&lt;script src="https://js.stripe.com/v3/"&gt;` on the iframe host page for the Payment Element.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
+          <t>Stripe.js is the one script that cannot be bundled. Stripe requires it to be loaded from `https://js.stripe.com/v3/` at page load and forbids self-hosting, because the library is what keeps card data out of the merchant's origin (PCI DSS SAQ A eligibility) and Stripe patches it in place without a version change. Loading a frozen copy would ship a payment library that is out of date the day it is built. The package confines the load to exactly these two Visualforce pages, which exist only to host the Payment Element in an iframe and to receive the 3-D Secure / bank-authentication redirect; no Lightning Web Component loads any external JavaScript or CSS.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>`grep -rn 'loadScript\|loadStyle' base/main/default/lwc` returns nothing, and these two pages are the only `&lt;script src=` in the package. `js.stripe.com` is a packaged CSP trusted site. The exception is written up as FP-9 in docs/security/appexchange-security-review-readiness.md, and the pages carry the reason in a comment beside the tag.</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/pages/stripePayment.page:53</t>
+          <t>base/main/default/pages/stripePaymentReturn.page:40</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>`&lt;script src="https://js.stripe.com/v3/"&gt;` on the iframe host page for the Payment Element.</t>
+          <t>Same tag on the 3-D Secure / bank-authentication return page, which must call Stripe.js to read the redirect result.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1869,65 +1869,8 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>R-025</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Working as designed</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>LoadJavaScriptHtmlScript</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>pmd</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>base/main/default/pages/stripePaymentReturn.page:40</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Javascript should always be loaded from static resources</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Stripe.js loaded from js.stripe.com in the two Visualforce payment pages</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Same tag on the 3-D Secure / bank-authentication return page, which must call Stripe.js to read the redirect result.</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Stripe.js is the one script that cannot be bundled. Stripe requires it to be loaded from `https://js.stripe.com/v3/` at page load and forbids self-hosting, because the library is what keeps card data out of the merchant's origin (PCI DSS SAQ A eligibility) and Stripe patches it in place without a version change. Loading a frozen copy would ship a payment library that is out of date the day it is built. The package confines the load to exactly these two Visualforce pages, which exist only to host the Payment Element in an iframe and to receive the 3-D Secure / bank-authentication redirect; no Lightning Web Component loads any external JavaScript or CSS.</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>`grep -rn 'loadScript\|loadStyle' base/main/default/lwc` returns nothing, and these two pages are the only `&lt;script src=` in the package. `js.stripe.com` is a packaged CSP trusted site. The exception is written up as FP-9 in docs/security/appexchange-security-review-readiness.md, and the pages carry the reason in a comment beside the tag.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K26"/>
+  <autoFilter ref="A1:K25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1988,7 +1931,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -1998,7 +1941,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2009,7 +1952,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>f37ab088</t>
+          <t>f2e4eb15</t>
         </is>
       </c>
     </row>
@@ -2021,7 +1964,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/code-analyzer-false-positives.xlsx
+++ b/assets/security-review/code-analyzer-false-positives.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Scan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Responses'!$A$1:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Responses'!$A$1:$M$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -438,10 +438,12 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="90" customWidth="1" min="10" max="10"/>
-    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="90" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="90" customWidth="1" min="11" max="11"/>
+    <col width="70" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,27 +479,37 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Scanner's claim</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Why the claim is false</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>At this site</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Why it is not a defect</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>How to verify</t>
+          <t>Supporting detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Sources</t>
         </is>
       </c>
     </row>
@@ -539,22 +551,34 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>The claim that this call "opens the door to several attacks" by disabling CRUD security is false. The call switches off only FFLib's own trigger-layer assertion, `fflib_SObjectDomain.Configuration.EnforcingTriggerCRUDSecurity`, a library check that the vendored base class layers above the platform. It changes nothing about how the DML executes: every write that fires this domain still runs under Salesforce's own object permissions, field-level security and sharing, which no Apex call can disable. This domain only recomputes `Designation__c` fund totals when a `Donation_Designation__c` row changes. That object is a master-detail detail of the standard Opportunity, so a second-generation package cannot ship an object permission on it and `isCreateable()` is false for every user without Modify All Data; with the library check left on, FFLib throws `Permission to create an Donation_Designation__c denied.` on a rollup the user is entitled to trigger, and the fund total silently stops updating. The constructor is the only site and carries its reason in the `// doc:` comment above it.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>Configuration.disableTriggerCRUDSecurity() in a rollup domain constructor</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Designation total rollup. Without the opt-out the rollup silently stops recomputing fund totals for non-admin users.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>The FFLib domain layer re-asserts `isCreateable()` on every record even when the DML is running in SYSTEM_MODE, which makes an internally-triggered rollup fail for any user who cannot directly create the rolled-up record. These two domains recompute totals only—`Designation__c` and recurring-donation aggregates—and the call scopes the opt-out to the FFLib trigger check alone. The DML itself still runs under the platform's rules; the platform's own CRUD, FLS and sharing enforcement is untouched. Without it, a non-admin donation write silently stops rolling up fund totals.</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Both call sites are annotated in place. In `RecurringDonations` the call sits behind an explicit `suppressTriggerCrudCheck` flag rather than being unconditional. The wider reasoning—that field permissions are inert without object access on a master-detail detail object—is written up in the Change Management section of AGENTS.md and in the `EventTicketTypesSelector` class header.</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.pmd-code.org/pmd-doc-7.26.0/pmd_rules_apex_security.html#apexdangerousmethods — "Checks against calling dangerous methods"; on `Configuration.disableTriggerCRUDSecurity()`: "Disabling CRUD security opens the door to several attacks and requires manual validation, which is unreliable."
+https://github.com/apex-enterprise-patterns/fflib-apex-common/blob/master/sfdx-source/apex-common/main/classes/fflib_SObjectDomain.cls — `Configuration.EnforcingTriggerCRUDSecurity` is documented as "True if the base class is checking the users CRUD requirements before invoking trigger methods"; `handleAfterInsert()` throws `DomainException('Permission to create an ' + name + ' denied.')` when it is on and `SObjectDescribe.isCreateable()` is false. It is a library check, not a platform setting.
+AGENTS.md, "Change Management — Locked Decisions Protocol": why a detail of a standard object cannot be granted by a 2GP permission set, so its field permissions are inert and `isCreateable()` is false for every non-admin user.</t>
         </is>
       </c>
     </row>
@@ -596,22 +620,34 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>The claim is false for the same reason: The call switches off only FFLib's own trigger-layer assertion, `fflib_SObjectDomain.Configuration.EnforcingTriggerCRUDSecurity`, a library check that the vendored base class layers above the platform. It changes nothing about how the DML executes: every write that fires this domain still runs under Salesforce's own object permissions, field-level security and sharing, which no Apex call can disable. The call is guarded by `suppressTriggerCrudCheck`, which only `CampaignService`'s donor-rollup commit sets, saving the prior value and restoring it in a `finally`. That commit writes three rollup fields on the donor Contact (`Total_Donated__c`, `Gift_Count__c`, `Last_Donation_Date__c`) after a gift is finalized, in the transaction of whoever saved the gift, including the site guest user, who cannot hold Edit on Contact. The rollup values are computed server-side from the gift that was just committed; no caller-supplied value reaches the Contact, and the platform's own permission checks on the write are untouched.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>Configuration.disableTriggerCRUDSecurity() in a rollup domain constructor</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Donor rollup (Total_Donated__c, Gift_Count__c, Last_Donation_Date__c), behind `suppressTriggerCrudCheck`, which only CampaignService's rollup commit sets and restores in `finally`. Without it a staff user who can edit a donation but not a Contact cannot close a gift.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>The FFLib domain layer re-asserts `isCreateable()` on every record even when the DML is running in SYSTEM_MODE, which makes an internally-triggered rollup fail for any user who cannot directly create the rolled-up record. These two domains recompute totals only—`Designation__c` and recurring-donation aggregates—and the call scopes the opt-out to the FFLib trigger check alone. The DML itself still runs under the platform's rules; the platform's own CRUD, FLS and sharing enforcement is untouched. Without it, a non-admin donation write silently stops rolling up fund totals.</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Both call sites are annotated in place. In `RecurringDonations` the call sits behind an explicit `suppressTriggerCrudCheck` flag rather than being unconditional. The wider reasoning—that field permissions are inert without object access on a master-detail detail object—is written up in the Change Management section of AGENTS.md and in the `EventTicketTypesSelector` class header.</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.pmd-code.org/pmd-doc-7.26.0/pmd_rules_apex_security.html#apexdangerousmethods — "Checks against calling dangerous methods"; on `Configuration.disableTriggerCRUDSecurity()`: "Disabling CRUD security opens the door to several attacks and requires manual validation, which is unreliable."
+https://github.com/apex-enterprise-patterns/fflib-apex-common/blob/master/sfdx-source/apex-common/main/classes/fflib_SObjectDomain.cls — `Configuration.EnforcingTriggerCRUDSecurity` is documented as "True if the base class is checking the users CRUD requirements before invoking trigger methods"; `handleAfterInsert()` throws `DomainException('Permission to create an ' + name + ' denied.')` when it is on and `SObjectDescribe.isCreateable()` is false. It is a library check, not a platform setting.
+AGENTS.md, "Change Management — Locked Decisions Protocol": why a detail of a standard object cannot be granted by a 2GP permission set, so its field permissions are inert and `isCreateable()` is false for every non-admin user.</t>
         </is>
       </c>
     </row>
@@ -653,22 +689,34 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>The claim is false for the same reason: The call switches off only FFLib's own trigger-layer assertion, `fflib_SObjectDomain.Configuration.EnforcingTriggerCRUDSecurity`, a library check that the vendored base class layers above the platform. It changes nothing about how the DML executes: every write that fires this domain still runs under Salesforce's own object permissions, field-level security and sharing, which no Apex call can disable. Here the call is not even unconditional. It runs only while the static `suppressTriggerCrudCheck` flag is true, and the sole code that sets the flag is the donor-portal path in `DonorPortalService` that updates a schedule on the donor's own behalf, which sets it immediately before the commit and clears it in the next statement. In every other transaction the FFLib assertion stays on. The donor is authorized by a verified access code before that path is reached, and the guest user it runs as cannot hold Edit on the object at all (a platform limit of the guest licence), which is exactly why the library check would otherwise block a legitimate update.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>Configuration.disableTriggerCRUDSecurity() in a rollup domain constructor</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Same call, behind the explicit `suppressTriggerCrudCheck` flag rather than unconditional.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>The FFLib domain layer re-asserts `isCreateable()` on every record even when the DML is running in SYSTEM_MODE, which makes an internally-triggered rollup fail for any user who cannot directly create the rolled-up record. These two domains recompute totals only—`Designation__c` and recurring-donation aggregates—and the call scopes the opt-out to the FFLib trigger check alone. The DML itself still runs under the platform's rules; the platform's own CRUD, FLS and sharing enforcement is untouched. Without it, a non-admin donation write silently stops rolling up fund totals.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Both call sites are annotated in place. In `RecurringDonations` the call sits behind an explicit `suppressTriggerCrudCheck` flag rather than being unconditional. The wider reasoning—that field permissions are inert without object access on a master-detail detail object—is written up in the Change Management section of AGENTS.md and in the `EventTicketTypesSelector` class header.</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.pmd-code.org/pmd-doc-7.26.0/pmd_rules_apex_security.html#apexdangerousmethods — "Checks against calling dangerous methods"; on `Configuration.disableTriggerCRUDSecurity()`: "Disabling CRUD security opens the door to several attacks and requires manual validation, which is unreliable."
+https://github.com/apex-enterprise-patterns/fflib-apex-common/blob/master/sfdx-source/apex-common/main/classes/fflib_SObjectDomain.cls — `Configuration.EnforcingTriggerCRUDSecurity` is documented as "True if the base class is checking the users CRUD requirements before invoking trigger methods"; `handleAfterInsert()` throws `DomainException('Permission to create an ' + name + ' denied.')` when it is on and `SObjectDescribe.isCreateable()` is false. It is a library check, not a platform setting.
+AGENTS.md, "Change Management — Locked Decisions Protocol": why a detail of a standard object cannot be granted by a 2GP permission set, so its field permissions are inert and `isCreateable()` is false for every non-admin user.</t>
         </is>
       </c>
     </row>
@@ -685,7 +733,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AvoidHardcodedCredentialsInVarAssign</t>
+          <t>ProtectSensitiveData</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -700,32 +748,45 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/classes/setup/controller/PostInstallHandler.cls:254</t>
+          <t>base/main/default/objects/Campaign_Design__c/fields/Theme_Tokens_JSON__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Hard coded credentials assigned to variable: Email_Signature__c  matched the token: SIGNATURE</t>
+          <t>Theme_Tokens_JSON__c is a potential auth token in a custom object: Campaign_Design__c</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Identifiers named credential / signature that hold no secret</t>
+          <t>The claim that this field "is a potential auth token" is false: the rule matched on the substring *token*, and the field is a Long Text Area holding a JSON map of CSS custom-property overrides (design tokens such as a button colour or a heading font) for a fundraising page design. The service layer filters every key against a packaged catalog (`Theme_Token__mdt`) and rejects unsafe values before a page reads it. It is admin-edited presentation data on a per-design record; it authenticates nothing and could not be stored in a protected setting.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Seeds `Settings__c.Email_Signature__c` with `'The &lt;org name&gt; team'` on first install — an email sign-off.</t>
+          <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>The one remaining site is the identifier pattern matching a name, not a value: `PostInstallHandler` seeds `Settings__c.Email_Signature__c` with `'The &lt;org name&gt; team'` on first install — *signature* there is the closing line of an outbound email, and the field's API name is packaged and cannot be renamed. The other eight hits this rule used to produce were cleared on 2026-09-25 by renaming the identifiers to say what they hold (`donorEndpoint` / `adminEndpoint` for `'callout:' + &lt;Named Credential name&gt;`, `AWAITING_SETUP_LABEL`, `DEFAULT_EMAIL_CLOSING`, `holderName` / `roleSummary`). No secret material exists anywhere in package source: the only place a Stripe key lives is inside a Named Credential the subscriber builds in Setup, which Apex cannot read back.</t>
+          <t>CSS design-token overrides as JSON; *token* means a CSS custom property.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>`Payment_Account__c.Stripe_*_Restricted_Key__c` are Text(80) fields whose `&lt;description&gt;` states they hold a Named Credential name, consumed as `'callout:' + name`. `scripts/lint/security-review-scan.py` inventories every `key`/`token`/`secret`-named field on each CI run against a baseline. The Named-Credential-only rule is FP-4 in docs/security/appexchange-security-review-readiness.md.</t>
+          <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar, class `com.salesforce.security.pmd.xml.DetectSecretsInCustomObjects`): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." It is keyed on the field's API name, which is why an ordinary word that contains *sign*, *auth*, *token* or *credit* is reported with the message "is a potential auth token".
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — the Trailhead module the rule description refers to; it defines the remediation as storing "API keys or other secret keys" in protected custom metadata or protected custom settings. None of these fields holds a key.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/objects/&lt;Object&gt;/fields/&lt;Field&gt;.field-meta.xml — each flagged field's `&lt;description&gt;` and `&lt;inlineHelpText&gt;` state what it holds.</t>
         </is>
       </c>
     </row>
@@ -757,32 +818,45 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Campaign_Design__c/fields/Theme_Tokens_JSON__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Donation_Designation__c/fields/Designation__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Theme_Tokens_JSON__c is a potential auth token in a custom object: Campaign_Design__c</t>
+          <t>Designation__c is a potential auth token in a custom object: Donation_Designation__c</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>The claim that this field "is a potential auth token" is false: the rule matched on the substring *sign* inside *Designation*, the fundraising term for the fund or program a gift is earmarked to. The field is a lookup to a `Designation__c` record on the row that records one split of a gift. A relationship field holds a record Id, not a secret.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>CSS design-token overrides as JSON; *token* means a CSS custom property.</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>Lookup to the fund a gift split supports; matches on *sign*.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar, class `com.salesforce.security.pmd.xml.DetectSecretsInCustomObjects`): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." It is keyed on the field's API name, which is why an ordinary word that contains *sign*, *auth*, *token* or *credit* is reported with the message "is a potential auth token".
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — the Trailhead module the rule description refers to; it defines the remediation as storing "API keys or other secret keys" in protected custom metadata or protected custom settings. None of these fields holds a key.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/objects/&lt;Object&gt;/fields/&lt;Field&gt;.field-meta.xml — each flagged field's `&lt;description&gt;` and `&lt;inlineHelpText&gt;` state what it holds.</t>
         </is>
       </c>
     </row>
@@ -794,7 +868,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Working as designed</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -814,32 +888,46 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Donation_Designation__c/fields/Designation__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Donation_Staging__c/fields/Access_Token__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Designation__c is a potential auth token in a custom object: Donation_Designation__c</t>
+          <t>Access_Token__c is a potential auth token in a custom object: Donation_Staging__c</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Field names that merely contain sign, auth, token or credit</t>
+          <t>The claim that this value should be stored in a protected custom setting is false because it is not an org-wide secret and no setting could hold it: it is a per-record capability token minted server-side for one guest checkout. It is a 256-bit random value (`SecureTokens.opaque()`, 64 hex characters) written to a unique external-Id field on the staging row, scopes three guest actions to that single row, cannot address any other record, and dies with the row when the checkout completes or the staging retention job purges it. Its entropy, expiry, single-use, revocation and guest-FLS properties are written in the field's `&lt;description&gt;` and tabulated in FP-16 of the readiness document. Holding it in a protected setting would make it org-wide, which is the opposite of the control it provides.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Lookup to the fund a gift split supports; matches on *sign*.</t>
+          <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
+          <t>256-bit random capability token scoped to one staging row; properties in FP-16.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." A protected setting is org-wide configuration; these fields are per-record transaction state, so the remediation cannot apply.
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — protected custom settings and protected custom metadata are the module's stores for "API keys or other secret keys"; a per-checkout nonce or a hash of a one-time code is neither.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.
+docs/security/appexchange-security-review-readiness.md, FP-16 — the token table: entropy, expiry, single-use, revocation and guest-FLS posture for every URL-borne token.</t>
         </is>
       </c>
     </row>
@@ -871,32 +959,46 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Donation_Staging__c/fields/Access_Token__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Donation_Staging__c/fields/Idempotency_Key__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Access_Token__c is a potential auth token in a custom object: Donation_Staging__c</t>
+          <t>Idempotency_Key__c is a potential auth token in a custom object: Donation_Staging__c</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>The claim is false because the field holds a client-generated identifier for one ticket-checkout attempt, not a credential: its only job is to make a double-submit reuse the first attempt instead of charging twice. Possessing the value grants nothing, it is never used to authorise a read or a write, and the unique external-Id index on it is the race backstop. It is per-record transaction state and cannot live in an org-wide setting.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>256-bit random capability token scoped to one staging row; properties in FP-16.</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>Client-generated ticket-checkout attempt id; unique index is the double-submit backstop.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." A protected setting is org-wide configuration; these fields are per-record transaction state, so the remediation cannot apply.
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — protected custom settings and protected custom metadata are the module's stores for "API keys or other secret keys"; a per-checkout nonce or a hash of a one-time code is neither.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.
+docs/security/appexchange-security-review-readiness.md, FP-16 — the token table: entropy, expiry, single-use, revocation and guest-FLS posture for every URL-borne token.</t>
         </is>
       </c>
     </row>
@@ -928,32 +1030,46 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Donation_Staging__c/fields/Idempotency_Key__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Guest_Request__c/fields/Idempotency_Key__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Idempotency_Key__c is a potential auth token in a custom object: Donation_Staging__c</t>
+          <t>Idempotency_Key__c is a potential auth token in a custom object: Guest_Request__c</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>The claim is false for the same reason: the field is a client-generated request identifier on a queued donor request (a refund request, an attendee-naming request) so that a double-click cannot queue the same work twice. It authorises nothing; the request itself is authorised by the donor's verified portal access code before the row is created. A per-request nonce cannot be an org-wide protected setting.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Client-generated ticket-checkout attempt id; unique index is the double-submit backstop.</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>Client-generated request id so a double-click cannot queue the same work twice.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." A protected setting is org-wide configuration; these fields are per-record transaction state, so the remediation cannot apply.
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — protected custom settings and protected custom metadata are the module's stores for "API keys or other secret keys"; a per-checkout nonce or a hash of a one-time code is neither.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.
+docs/security/appexchange-security-review-readiness.md, FP-16 — the token table: entropy, expiry, single-use, revocation and guest-FLS posture for every URL-borne token.</t>
         </is>
       </c>
     </row>
@@ -985,32 +1101,46 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Guest_Request__c/fields/Idempotency_Key__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Payment_Account__c/fields/Publishable_Key__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Idempotency_Key__c is a potential auth token in a custom object: Guest_Request__c</t>
+          <t>Publishable_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
+          <t>The claim that this field holds a secret that belongs in a protected setting is false: it holds Stripe's publishable key (`pk_…`), which Stripe documents as safe to expose and designed to be included in front-end code. It can only identify the account and create payment tokens from card details the donor is typing; it cannot create charges, issue refunds or read account data. The package sends it to every donor's browser by construction, because Stripe.js cannot mount the payment form without it. A protected setting exists to hide a value from the subscriber; this value is published on every donation page on purpose. The secret and restricted keys that do authorise charges and refunds are never in any field.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Client-generated request id so a double-click cannot queue the same work twice.</t>
+          <t>Fields that hold a Named Credential's name, not a key</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
+          <t>Stripe publishable key — designed to be sent to the browser; secret key is never in a field.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+          <t>`Stripe_Donor_Restricted_Key__c` and `Stripe_Admin_Restricted_Key__c` are Text(80) fields holding the **API name** of a Named Credential the subscriber admin built by hand in Setup, and Apex consumes them as `'callout:' + name`. The key itself is inside the Named Credential and is never readable from Apex, a field, or the UI. The fields are per-Payment-Account rather than org-wide because one org can run several gateway accounts (for example one per legal entity), which a hierarchy setting cannot model. `Publishable_Key__c` holds Stripe's publishable key, which Stripe designs to be embedded in browser-side code and is sent to every donor's browser by construction; it authorises nothing on its own.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. AGENTS.md Rule 9 makes this the required pattern, and FP-4 in docs/security/appexchange-security-review-readiness.md documents it for the reviewer.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.stripe.com/keys — the publishable key (`pk_…`) is "Safe to expose: Yes … It can identify your account and create tokens or PaymentMethods from payment details, but it can't perform sensitive operations such as creating charges or reading account data. You can include it in front-end code"; restricted and secret keys are not safe to expose and "Don't put keys in source code or configuration files."
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — Named Credentials are "a mechanism for securely managing authentication values for external providers and services"; the module's remediation for an API key is a Named Credential or a protected setting, which is exactly where the key lives here.
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_callouts_named_credentials.htm — Apex callouts through Named Credentials (`callout:&lt;name&gt;`), the construction `StripeGateway.cls` uses (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/classes/payment/gateway/StripeGateway.cls — `this.donorEndpoint = 'callout:' + acct.Stripe_Donor_Restricted_Key__c;` and the matching admin line: the field value is a Named Credential name.
+docs/security/appexchange-security-review-readiness.md, FP-4 — the Named-Credentials-only rule and the reviewer-facing write-up.</t>
         </is>
       </c>
     </row>
@@ -1042,32 +1172,46 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Payment_Account__c/fields/Publishable_Key__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Payment_Account__c/fields/Stripe_Admin_Restricted_Key__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Publishable_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
+          <t>Stripe_Admin_Restricted_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>The claim that this field is "a potential auth token" that should move to a protected setting is false: the field is a Text(80) that holds the API name of a Named Credential, not a key. The subscriber administrator builds that Named Credential by hand in Setup and pastes the restricted key into it; the package consumes the field as `'callout:' + name` and can never read the key back, which is exactly the Named Credential pattern the rule's remediation guidance describes. The field's `&lt;description&gt;` states that it holds a name and that an unrestricted secret key is not an acceptable value for the credential behind it. It is per payment account rather than org-wide because one organisation can run several gateway accounts, which a hierarchy setting cannot model.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>Fields that hold a Named Credential's name, not a key</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Stripe publishable key — designed to be sent to the browser; secret key is never in a field.</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t>Text(80): API name of the Named Credential holding the back-office restricted key.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>`Stripe_Donor_Restricted_Key__c` and `Stripe_Admin_Restricted_Key__c` are Text(80) fields holding the **API name** of a Named Credential the subscriber admin built by hand in Setup, and Apex consumes them as `'callout:' + name`. The key itself is inside the Named Credential and is never readable from Apex, a field, or the UI. The fields are per-Payment-Account rather than org-wide because one org can run several gateway accounts (for example one per legal entity), which a hierarchy setting cannot model. `Publishable_Key__c` holds Stripe's publishable key, which Stripe designs to be embedded in browser-side code and is sent to every donor's browser by construction; it authorises nothing on its own.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. AGENTS.md Rule 9 makes this the required pattern, and FP-4 in docs/security/appexchange-security-review-readiness.md documents it for the reviewer.</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.stripe.com/keys — the publishable key (`pk_…`) is "Safe to expose: Yes … It can identify your account and create tokens or PaymentMethods from payment details, but it can't perform sensitive operations such as creating charges or reading account data. You can include it in front-end code"; restricted and secret keys are not safe to expose and "Don't put keys in source code or configuration files."
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — Named Credentials are "a mechanism for securely managing authentication values for external providers and services"; the module's remediation for an API key is a Named Credential or a protected setting, which is exactly where the key lives here.
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_callouts_named_credentials.htm — Apex callouts through Named Credentials (`callout:&lt;name&gt;`), the construction `StripeGateway.cls` uses (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/classes/payment/gateway/StripeGateway.cls — `this.donorEndpoint = 'callout:' + acct.Stripe_Donor_Restricted_Key__c;` and the matching admin line: the field value is a Named Credential name.
+docs/security/appexchange-security-review-readiness.md, FP-4 — the Named-Credentials-only rule and the reviewer-facing write-up.</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1243,46 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Payment_Account__c/fields/Stripe_Admin_Restricted_Key__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Payment_Account__c/fields/Stripe_Donor_Restricted_Key__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Stripe_Admin_Restricted_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
+          <t>Stripe_Donor_Restricted_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>The claim is false for the same reason: the field is a Text(80) holding the API name of the Named Credential that carries the charge-only restricted key, consumed as `'callout:' + acct.Stripe_Donor_Restricted_Key__c` in `StripeGateway.cls`. The key itself lives only inside the Named Credential the administrator built in Setup and is not readable from Apex, from the field or from any UI. Moving the field to a protected setting would move a credential name, not a secret, and would lose the per-account scope.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>Fields that hold a Named Credential's name, not a key</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Text(80): API name of the Named Credential holding the back-office restricted key.</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>Text(80): API name of the Named Credential holding the charge-only restricted key.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>`Stripe_Donor_Restricted_Key__c` and `Stripe_Admin_Restricted_Key__c` are Text(80) fields holding the **API name** of a Named Credential the subscriber admin built by hand in Setup, and Apex consumes them as `'callout:' + name`. The key itself is inside the Named Credential and is never readable from Apex, a field, or the UI. The fields are per-Payment-Account rather than org-wide because one org can run several gateway accounts (for example one per legal entity), which a hierarchy setting cannot model. `Publishable_Key__c` holds Stripe's publishable key, which Stripe designs to be embedded in browser-side code and is sent to every donor's browser by construction; it authorises nothing on its own.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. AGENTS.md Rule 9 makes this the required pattern, and FP-4 in docs/security/appexchange-security-review-readiness.md documents it for the reviewer.</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.stripe.com/keys — the publishable key (`pk_…`) is "Safe to expose: Yes … It can identify your account and create tokens or PaymentMethods from payment details, but it can't perform sensitive operations such as creating charges or reading account data. You can include it in front-end code"; restricted and secret keys are not safe to expose and "Don't put keys in source code or configuration files."
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — Named Credentials are "a mechanism for securely managing authentication values for external providers and services"; the module's remediation for an API key is a Named Credential or a protected setting, which is exactly where the key lives here.
+https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_callouts_named_credentials.htm — Apex callouts through Named Credentials (`callout:&lt;name&gt;`), the construction `StripeGateway.cls` uses (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/classes/payment/gateway/StripeGateway.cls — `this.donorEndpoint = 'callout:' + acct.Stripe_Donor_Restricted_Key__c;` and the matching admin line: the field value is a Named Credential name.
+docs/security/appexchange-security-review-readiness.md, FP-4 — the Named-Credentials-only rule and the reviewer-facing write-up.</t>
         </is>
       </c>
     </row>
@@ -1156,32 +1314,46 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Payment_Account__c/fields/Stripe_Donor_Restricted_Key__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Portal_Access_Token__c/fields/Code_Hash__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Stripe_Donor_Restricted_Key__c is a potential auth token in a custom object: Payment_Account__c</t>
+          <t>Code_Hash__c is a potential auth token in a custom object: Portal_Access_Token__c</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Fields that hold a Named Credential's name, not a key</t>
+          <t>The claim is false because the field stores the SHA-256 hash of the emailed sign-in code, never the code itself: `DonorPortalService` writes `Code_Hash__c = hashToken(rawCode)` when a code is issued and sets `Code_Hash__c = null` the moment it is redeemed, so a stored value can neither reveal the code nor be replayed. Storing a hash in place of a secret is the control the rule exists to encourage, and a per-donor one-time code could not be an org-wide protected setting.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Text(80): API name of the Named Credential holding the charge-only restricted key.</t>
+          <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>`Stripe_Donor_Restricted_Key__c` and `Stripe_Admin_Restricted_Key__c` are Text(80) fields holding the **API name** of a Named Credential the subscriber admin built by hand in Setup, and Apex consumes them as `'callout:' + name`. The key itself is inside the Named Credential and is never readable from Apex, a field, or the UI. The fields are per-Payment-Account rather than org-wide because one org can run several gateway accounts (for example one per legal entity), which a hierarchy setting cannot model. `Publishable_Key__c` holds Stripe's publishable key, which Stripe designs to be embedded in browser-side code and is sent to every donor's browser by construction; it authorises nothing on its own.</t>
+          <t>SHA-256 of the emailed sign-in code, nulled on redemption; the code itself is never stored.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. AGENTS.md Rule 9 makes this the required pattern, and FP-4 in docs/security/appexchange-security-review-readiness.md documents it for the reviewer.</t>
+          <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." A protected setting is org-wide configuration; these fields are per-record transaction state, so the remediation cannot apply.
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — protected custom settings and protected custom metadata are the module's stores for "API keys or other secret keys"; a per-checkout nonce or a hash of a one-time code is neither.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.
+docs/security/appexchange-security-review-readiness.md, FP-16 — the token table: entropy, expiry, single-use, revocation and guest-FLS posture for every URL-borne token.</t>
         </is>
       </c>
     </row>
@@ -1213,32 +1385,46 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Portal_Access_Token__c/fields/Code_Hash__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Portal_Access_Token__c/fields/Session_Hash__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Code_Hash__c is a potential auth token in a custom object: Portal_Access_Token__c</t>
+          <t>Session_Hash__c is a potential auth token in a custom object: Portal_Access_Token__c</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>The claim is false because the field stores the SHA-256 hash of the donor's browser session token (`Session_Hash__c = hashToken(sessionToken)`), never the token: the raw value exists only in the donor's browser, a per-request lookup compares hashes (`PortalAccessTokensSelector` selects on `Session_Hash__c = :sessionHash`), and the unique external-Id index keeps that lookup selective. The row expires on the configured session TTL and is revoked by deletion. A hash of a per-session value is not a secret and cannot be an org-wide setting.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>SHA-256 of the emailed sign-in code, nulled on redemption; the code itself is never stored.</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>SHA-256 of the browser session token, unique external Id; the token itself is never stored.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." A protected setting is org-wide configuration; these fields are per-record transaction state, so the remediation cannot apply.
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — protected custom settings and protected custom metadata are the module's stores for "API keys or other secret keys"; a per-checkout nonce or a hash of a one-time code is neither.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.
+docs/security/appexchange-security-review-readiness.md, FP-16 — the token table: entropy, expiry, single-use, revocation and guest-FLS posture for every URL-borne token.</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1436,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Working as designed</t>
+          <t>False positive</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1270,32 +1456,45 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Portal_Access_Token__c/fields/Session_Hash__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Recurring_Designation__c/fields/Designation__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Session_Hash__c is a potential auth token in a custom object: Portal_Access_Token__c</t>
+          <t>Designation__c is a potential auth token in a custom object: Recurring_Designation__c</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Per-record capability tokens, idempotency keys and SHA-256 hashes</t>
+          <t>The claim that this field "is a potential auth token" is false: the rule matched on *sign* inside *Designation*. The field is a lookup to the fund a recurring gift split supports, on the junction object between a recurring schedule and its funds. It is a record Id.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>SHA-256 of the browser session token, unique external Id; the token itself is never stored.</t>
+          <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>None of these is an org-wide secret, and none could live in a setting: each is per-record transactional state. `Donation_Staging__c.Access_Token__c` is a 256-bit random capability token minted server-side for one guest checkout; it scopes three guest actions to that single staging row, cannot read any other record, and dies with the row. `Idempotency_Key__c` on `Donation_Staging__c` and `Guest_Request__c` is a client-generated request identifier whose only job is to make a double-submit reuse the first attempt; possessing one grants nothing, and the unique index on it is the race backstop. `Portal_Access_Token__c.Code_Hash__c` and `Session_Hash__c` hold the SHA-256 of the emailed sign-in code and of the browser session token respectively — the raw value is never stored, the code hash is nulled the moment the code is redeemed, and the session hash is a unique external Id so a per-request lookup is selective. Storing hashes rather than values is precisely the control the rule is asking for.</t>
+          <t>Lookup to the fund a recurring split supports; matches on *sign*.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+          <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar, class `com.salesforce.security.pmd.xml.DetectSecretsInCustomObjects`): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." It is keyed on the field's API name, which is why an ordinary word that contains *sign*, *auth*, *token* or *credit* is reported with the message "is a potential auth token".
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — the Trailhead module the rule description refers to; it defines the remediation as storing "API keys or other secret keys" in protected custom metadata or protected custom settings. None of these fields holds a key.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/objects/&lt;Object&gt;/fields/&lt;Field&gt;.field-meta.xml — each flagged field's `&lt;description&gt;` and `&lt;inlineHelpText&gt;` state what it holds.</t>
         </is>
       </c>
     </row>
@@ -1327,32 +1526,45 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Recurring_Designation__c/fields/Designation__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Recurring_Donation__c/fields/Designation__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Designation__c is a potential auth token in a custom object: Recurring_Designation__c</t>
+          <t>Designation__c is a potential auth token in a custom object: Recurring_Donation__c</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>The claim that this field "is a potential auth token" is false: the rule matched on *sign* inside *Designation*. The field is the single-fund lookup on a recurring schedule, used when the schedule is not split across several funds. It is a record Id.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Lookup to the fund a recurring split supports; matches on *sign*.</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>Single-fund lookup on a recurring schedule; matches on *sign*.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar, class `com.salesforce.security.pmd.xml.DetectSecretsInCustomObjects`): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." It is keyed on the field's API name, which is why an ordinary word that contains *sign*, *auth*, *token* or *credit* is reported with the message "is a potential auth token".
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — the Trailhead module the rule description refers to; it defines the remediation as storing "API keys or other secret keys" in protected custom metadata or protected custom settings. None of these fields holds a key.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/objects/&lt;Object&gt;/fields/&lt;Field&gt;.field-meta.xml — each flagged field's `&lt;description&gt;` and `&lt;inlineHelpText&gt;` state what it holds.</t>
         </is>
       </c>
     </row>
@@ -1384,32 +1596,45 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Recurring_Donation__c/fields/Designation__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Recurring_Donation__c/fields/Re_Auth_Link_Sent_At__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Designation__c is a potential auth token in a custom object: Recurring_Donation__c</t>
+          <t>Re_Auth_Link_Sent_At__c is a potential auth token in a custom object: Recurring_Donation__c</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>The claim that this field "is a potential auth token" is false: the rule matched on *auth* inside *Re_Auth*, which here means re-authentication of a card payment, not an API credential. The field is a Date/Time recording when the donor was last emailed a reminder to complete 3-D Secure on-session for a renewal, so the reminder is not sent twice. A timestamp authorises nothing.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Single-fund lookup on a recurring schedule; matches on *sign*.</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>Timestamp of the last 3-D Secure reminder email; matches on *auth*.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar, class `com.salesforce.security.pmd.xml.DetectSecretsInCustomObjects`): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." It is keyed on the field's API name, which is why an ordinary word that contains *sign*, *auth*, *token* or *credit* is reported with the message "is a potential auth token".
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — the Trailhead module the rule description refers to; it defines the remediation as storing "API keys or other secret keys" in protected custom metadata or protected custom settings. None of these fields holds a key.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/objects/&lt;Object&gt;/fields/&lt;Field&gt;.field-meta.xml — each flagged field's `&lt;description&gt;` and `&lt;inlineHelpText&gt;` state what it holds.</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1666,45 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Recurring_Donation__c/fields/Re_Auth_Link_Sent_At__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Recurring_Donation__c/fields/Re_Auth_Required__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Re_Auth_Link_Sent_At__c is a potential auth token in a custom object: Recurring_Donation__c</t>
+          <t>Re_Auth_Required__c is a potential auth token in a custom object: Recurring_Donation__c</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>The claim that this field "is a potential auth token" is false: the rule matched on *auth* inside *Re_Auth*. The field is a Checkbox that marks a recurring schedule whose next renewal needs the donor to complete 3-D Secure on-session; it is set from the payment gateway's decline reason and cleared once the donor completes the challenge. A boolean flag is not a secret.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Timestamp of the last 3-D Secure reminder email; matches on *auth*.</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>Checkbox: the donor must complete 3-D Secure on-session; matches on *auth*.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar, class `com.salesforce.security.pmd.xml.DetectSecretsInCustomObjects`): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." It is keyed on the field's API name, which is why an ordinary word that contains *sign*, *auth*, *token* or *credit* is reported with the message "is a potential auth token".
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — the Trailhead module the rule description refers to; it defines the remediation as storing "API keys or other secret keys" in protected custom metadata or protected custom settings. None of these fields holds a key.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/objects/&lt;Object&gt;/fields/&lt;Field&gt;.field-meta.xml — each flagged field's `&lt;description&gt;` and `&lt;inlineHelpText&gt;` state what it holds.</t>
         </is>
       </c>
     </row>
@@ -1498,32 +1736,45 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Recurring_Donation__c/fields/Re_Auth_Required__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Settings__c/fields/Default_Designation__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Re_Auth_Required__c is a potential auth token in a custom object: Recurring_Donation__c</t>
+          <t>Default_Designation__c is a potential auth token in the object: Settings__c with public visibility</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>The claim that this field "is a potential auth token" is false: the rule matched on *sign* inside *Designation*. The field is an 18-character Text holding the record Id of the fallback fund a gift is credited to when the donor picks none; it is Text only because a hierarchy custom setting cannot declare a lookup. It is edited by an administrator in the Settings console and holds nothing secret.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Checkbox: the donor must complete 3-D Secure on-session; matches on *auth*.</t>
-        </is>
-      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>18-character Id of the fallback fund, stored as text because a Custom Setting cannot hold a lookup; matches on *sign*.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar, class `com.salesforce.security.pmd.xml.DetectSecretsInCustomObjects`): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." It is keyed on the field's API name, which is why an ordinary word that contains *sign*, *auth*, *token* or *credit* is reported with the message "is a potential auth token".
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — the Trailhead module the rule description refers to; it defines the remediation as storing "API keys or other secret keys" in protected custom metadata or protected custom settings. None of these fields holds a key.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/objects/&lt;Object&gt;/fields/&lt;Field&gt;.field-meta.xml — each flagged field's `&lt;description&gt;` and `&lt;inlineHelpText&gt;` state what it holds.</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1806,45 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Settings__c/fields/Default_Designation__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Settings__c/fields/Email_Signature__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Default_Designation__c is a potential auth token in the object: Settings__c with public visibility</t>
+          <t>Email_Signature__c is a potential auth token in the object: Settings__c with public visibility</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>The claim that this field "is a potential auth token" is false: the rule matched on *sign* inside *Signature*, which here is the sign-off line printed above the footer of every outbound email (for example "The Riverside Foundation team"). It is a short display string an administrator edits, seeded at install from the organisation name, and is sent to every donor by design.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18-character Id of the fallback fund, stored as text because a Custom Setting cannot hold a lookup; matches on *sign*.</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>Sign-off line printed above the footer of every outbound email.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar, class `com.salesforce.security.pmd.xml.DetectSecretsInCustomObjects`): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." It is keyed on the field's API name, which is why an ordinary word that contains *sign*, *auth*, *token* or *credit* is reported with the message "is a potential auth token".
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — the Trailhead module the rule description refers to; it defines the remediation as storing "API keys or other secret keys" in protected custom metadata or protected custom settings. None of these fields holds a key.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/objects/&lt;Object&gt;/fields/&lt;Field&gt;.field-meta.xml — each flagged field's `&lt;description&gt;` and `&lt;inlineHelpText&gt;` state what it holds.</t>
         </is>
       </c>
     </row>
@@ -1612,32 +1876,45 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Settings__c/fields/Email_Signature__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Settings__c/fields/Portal_Token_TTL_Hours__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Email_Signature__c is a potential auth token in the object: Settings__c with public visibility</t>
+          <t>Portal_Token_TTL_Hours__c is a potential auth token in the object: Settings__c with public visibility</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>The claim that this field "is a potential auth token" is false: the rule matched on *token*, but the field is a Number: the ceiling, in hours, on how long a donor-portal session may live before the donor must sign in again. It is a configuration value an administrator sets; it contains no token.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Sign-off line printed above the footer of every outbound email.</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>A number of hours — the ceiling on a donor-portal session's lifetime.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
           <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar, class `com.salesforce.security.pmd.xml.DetectSecretsInCustomObjects`): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." It is keyed on the field's API name, which is why an ordinary word that contains *sign*, *auth*, *token* or *credit* is reported with the message "is a potential auth token".
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — the Trailhead module the rule description refers to; it defines the remediation as storing "API keys or other secret keys" in protected custom metadata or protected custom settings. None of these fields holds a key.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/objects/&lt;Object&gt;/fields/&lt;Field&gt;.field-meta.xml — each flagged field's `&lt;description&gt;` and `&lt;inlineHelpText&gt;` state what it holds.</t>
         </is>
       </c>
     </row>
@@ -1669,32 +1946,45 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Settings__c/fields/Portal_Token_TTL_Hours__c.field-meta.xml:1</t>
+          <t>base/main/default/objects/Settings__c/fields/Soft_Credit_Automation_Enabled__c.field-meta.xml:1</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Portal_Token_TTL_Hours__c is a potential auth token in the object: Settings__c with public visibility</t>
+          <t>Soft_Credit_Automation_Enabled__c is a potential auth token in the object: Settings__c with public visibility</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>The claim that this field "is a potential auth token" is false: the rule matched on *credit*, which here is the fundraising term soft credit (crediting a second person for influencing a gift), not a payment card. The field is a Checkbox that turns the soft-credit rollup on or off. A feature toggle is not a secret.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
           <t>Field names that merely contain sign, auth, token or credit</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>A number of hours — the ceiling on a donor-portal session's lifetime.</t>
-        </is>
-      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>Feature toggle for soft-credit rollups; matches on *credit*.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar, class `com.salesforce.security.pmd.xml.DetectSecretsInCustomObjects`): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." It is keyed on the field's API name, which is why an ordinary word that contains *sign*, *auth*, *token* or *credit* is reported with the message "is a potential auth token".
+https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — the Trailhead module the rule description refers to; it defines the remediation as storing "API keys or other secret keys" in protected custom metadata or protected custom settings. None of these fields holds a key.
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/objects/&lt;Object&gt;/fields/&lt;Field&gt;.field-meta.xml — each flagged field's `&lt;description&gt;` and `&lt;inlineHelpText&gt;` state what it holds.</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1996,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>False positive</t>
+          <t>Working as designed</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>ProtectSensitiveData</t>
+          <t>LoadJavaScriptHtmlScript</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1721,37 +2011,50 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/objects/Settings__c/fields/Soft_Credit_Automation_Enabled__c.field-meta.xml:1</t>
+          <t>base/main/default/pages/stripePayment.page:53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Soft_Credit_Automation_Enabled__c is a potential auth token in the object: Settings__c with public visibility</t>
+          <t>Javascript should always be loaded from static resources</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Field names that merely contain sign, auth, token or credit</t>
+          <t>The claim that this script must be loaded from a static resource is false because Stripe forbids it: Stripe's integration documentation requires Stripe.js to be loaded directly from `https://js.stripe.com` and never bundled or self-hosted. The library is what keeps card data out of the merchant's origin, which is the basis of the package's PCI SAQ A eligibility, and Stripe patches it in place without a version change; a copy frozen into a static resource would be a payment library that is out of date the day the package is built and would void that eligibility. The page exists only to host the Stripe Payment Element in an iframe, the host `js.stripe.com` is declared as a packaged CSP trusted site, and the tag is preceded by a comment that states this reason. No Lightning Web Component in the package loads any external script.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Feature toggle for soft-credit rollups; matches on *credit*.</t>
+          <t>Stripe.js loaded from js.stripe.com in the two Visualforce payment pages</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>These fields match on a substring of an ordinary English word and carry nothing sensitive. `Designation__c` and `Default_Designation__c` (the fund a gift is earmarked for) and `Campaign_Design__c.Theme_Tokens_JSON__c` match on *sign* and *token* — one is a lookup to a program, the other is a JSON map of CSS design-token overrides that the service layer filters against a packaged catalog. `Email_Signature__c` is the sign-off line printed on outbound email. `Re_Auth_Required__c` and `Re_Auth_Link_Sent_At__c` match on *auth* and are a checkbox and a timestamp recording that a donor must complete 3-D Secure on-session for a renewal and when they were last reminded. `Portal_Token_TTL_Hours__c` is a number of hours. `Soft_Credit_Automation_Enabled__c` matches on *credit* and is a feature toggle for soft-credit rollups; it has nothing to do with a payment card. A Protected Custom Setting could not hold any of them: they are per-record business data, and the two on `Settings__c` are admin-visible configuration that the Settings console edits.</t>
+          <t>`&lt;script src="https://js.stripe.com/v3/"&gt;` on the iframe host page for the Payment Element.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Stripe.js is the one script that cannot be bundled. Stripe requires it to be loaded from `https://js.stripe.com/v3/` at page load and forbids self-hosting, because the library is what keeps card data out of the merchant's origin (PCI DSS SAQ A eligibility) and Stripe patches it in place without a version change. Loading a frozen copy would ship a payment library that is out of date the day it is built. The package confines the load to exactly these two Visualforce pages, which exist only to host the Payment Element in an iframe and to receive the 3-D Secure / bank-authentication redirect; no Lightning Web Component loads any external JavaScript or CSS.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>`grep -rn 'loadScript\|loadStyle' base/main/default/lwc` returns nothing, and these two pages are the only `&lt;script src=` in the package. `js.stripe.com` is a packaged CSP trusted site. The exception is written up as FP-9 in docs/security/appexchange-security-review-readiness.md, and the pages carry the reason in a comment beside the tag.</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.stripe.com/js/including — "Include the Stripe.js script on each page of your site—it should always be loaded directly from https://js.stripe.com, rather than included in a bundle or hosted yourself."
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#loadjavascripthtmlscript — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/cspTrustedSites/Stripe_js.cspTrustedSite-meta.xml — `js.stripe.com` is a packaged CSP trusted site, so the load is declared to the platform rather than slipped past it.
+docs/security/appexchange-security-review-readiness.md, FP-9 — the standing exception and its PCI reasoning.</t>
         </is>
       </c>
     </row>
@@ -1783,7 +2086,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>base/main/default/pages/stripePayment.page:53</t>
+          <t>base/main/default/pages/stripePaymentReturn.page:40</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1793,84 +2096,40 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>The claim is false for the same reason: Stripe requires Stripe.js to be loaded from `https://js.stripe.com` and forbids self-hosting. This page is the return target of a 3-D Secure or bank-authentication redirect and must call Stripe.js to read the redirect result; it has no other content. The host is a packaged CSP trusted site, the reason is written in a comment beside the tag, and no other `&lt;script src&gt;` exists in the package.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>Stripe.js loaded from js.stripe.com in the two Visualforce payment pages</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>`&lt;script src="https://js.stripe.com/v3/"&gt;` on the iframe host page for the Payment Element.</t>
-        </is>
-      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>Same tag on the 3-D Secure / bank-authentication return page, which must call Stripe.js to read the redirect result.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>Stripe.js is the one script that cannot be bundled. Stripe requires it to be loaded from `https://js.stripe.com/v3/` at page load and forbids self-hosting, because the library is what keeps card data out of the merchant's origin (PCI DSS SAQ A eligibility) and Stripe patches it in place without a version change. Loading a frozen copy would ship a payment library that is out of date the day it is built. The package confines the load to exactly these two Visualforce pages, which exist only to host the Payment Element in an iframe and to receive the 3-D Secure / bank-authentication redirect; no Lightning Web Component loads any external JavaScript or CSS.</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>`grep -rn 'loadScript\|loadStyle' base/main/default/lwc` returns nothing, and these two pages are the only `&lt;script src=` in the package. `js.stripe.com` is a packaged CSP trusted site. The exception is written up as FP-9 in docs/security/appexchange-security-review-readiness.md, and the pages carry the reason in a comment beside the tag.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>R-024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Working as designed</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>LoadJavaScriptHtmlScript</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>pmd</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>base/main/default/pages/stripePaymentReturn.page:40</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Javascript should always be loaded from static resources</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Stripe.js loaded from js.stripe.com in the two Visualforce payment pages</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Same tag on the 3-D Secure / bank-authentication return page, which must call Stripe.js to read the redirect result.</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Stripe.js is the one script that cannot be bundled. Stripe requires it to be loaded from `https://js.stripe.com/v3/` at page load and forbids self-hosting, because the library is what keeps card data out of the merchant's origin (PCI DSS SAQ A eligibility) and Stripe patches it in place without a version change. Loading a frozen copy would ship a payment library that is out of date the day it is built. The package confines the load to exactly these two Visualforce pages, which exist only to host the Payment Element in an iframe and to receive the 3-D Secure / bank-authentication redirect; no Lightning Web Component loads any external JavaScript or CSS.</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>`grep -rn 'loadScript\|loadStyle' base/main/default/lwc` returns nothing, and these two pages are the only `&lt;script src=` in the package. `js.stripe.com` is a packaged CSP trusted site. The exception is written up as FP-9 in docs/security/appexchange-security-review-readiness.md, and the pages carry the reason in a comment beside the tag.</t>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.stripe.com/js/including — "Include the Stripe.js script on each page of your site—it should always be loaded directly from https://js.stripe.com, rather than included in a bundle or hosted yourself."
+https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#loadjavascripthtmlscript — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
+base/main/default/cspTrustedSites/Stripe_js.cspTrustedSite-meta.xml — `js.stripe.com` is a packaged CSP trusted site, so the load is declared to the platform rather than slipped past it.
+docs/security/appexchange-security-review-readiness.md, FP-9 — the standing exception and its PCI reasoning.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K25"/>
+  <autoFilter ref="A1:M24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1931,7 +2190,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -1941,7 +2200,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1952,7 +2211,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>f2e4eb15</t>
+          <t>e51c2601</t>
         </is>
       </c>
     </row>
@@ -1964,7 +2223,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/code-analyzer-false-positives.xlsx
+++ b/assets/security-review/code-analyzer-false-positives.xlsx
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>e51c2601</t>
+          <t>596d1eb8</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/code-analyzer-false-positives.xlsx
+++ b/assets/security-review/code-analyzer-false-positives.xlsx
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>596d1eb8</t>
+          <t>9279d2db</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/code-analyzer-false-positives.xlsx
+++ b/assets/security-review/code-analyzer-false-positives.xlsx
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9279d2db</t>
+          <t>36949d12</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>

--- a/assets/security-review/code-analyzer-false-positives.xlsx
+++ b/assets/security-review/code-analyzer-false-positives.xlsx
@@ -571,14 +571,14 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Both call sites are annotated in place. In `RecurringDonations` the call sits behind an explicit `suppressTriggerCrudCheck` flag rather than being unconditional. The wider reasoning—that field permissions are inert without object access on a master-detail detail object—is written up in the Change Management section of AGENTS.md and in the `EventTicketTypesSelector` class header.</t>
+          <t>Both call sites are annotated in place. In `RecurringDonations` the call sits behind an explicit `suppressTriggerCrudCheck` flag rather than being unconditional. The wider reasoning—that field permissions are inert without object access on a master-detail detail object—is written in the `EventTicketTypesSelector` class header, which ships in the package: a detail of a standard object cannot be granted by a packaged permission set (Salesforce ignores standard-object permissions at install, cited below), so its field permissions are inert and `isCreateable()` is false for every user without Modify All Data.</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>https://docs.pmd-code.org/pmd-doc-7.26.0/pmd_rules_apex_security.html#apexdangerousmethods — "Checks against calling dangerous methods"; on `Configuration.disableTriggerCRUDSecurity()`: "Disabling CRUD security opens the door to several attacks and requires manual validation, which is unreliable."
 https://github.com/apex-enterprise-patterns/fflib-apex-common/blob/master/sfdx-source/apex-common/main/classes/fflib_SObjectDomain.cls — `Configuration.EnforcingTriggerCRUDSecurity` is documented as "True if the base class is checking the users CRUD requirements before invoking trigger methods"; `handleAfterInsert()` throws `DomainException('Permission to create an ' + name + ' denied.')` when it is on and `SObjectDescribe.isCreateable()` is false. It is a library check, not a platform setting.
-AGENTS.md, "Change Management — Locked Decisions Protocol": why a detail of a standard object cannot be granted by a 2GP permission set, so its field permissions are inert and `isCreateable()` is false for every non-admin user.</t>
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Both call sites are annotated in place. In `RecurringDonations` the call sits behind an explicit `suppressTriggerCrudCheck` flag rather than being unconditional. The wider reasoning—that field permissions are inert without object access on a master-detail detail object—is written up in the Change Management section of AGENTS.md and in the `EventTicketTypesSelector` class header.</t>
+          <t>Both call sites are annotated in place. In `RecurringDonations` the call sits behind an explicit `suppressTriggerCrudCheck` flag rather than being unconditional. The wider reasoning—that field permissions are inert without object access on a master-detail detail object—is written in the `EventTicketTypesSelector` class header, which ships in the package: a detail of a standard object cannot be granted by a packaged permission set (Salesforce ignores standard-object permissions at install, cited below), so its field permissions are inert and `isCreateable()` is false for every user without Modify All Data.</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>https://docs.pmd-code.org/pmd-doc-7.26.0/pmd_rules_apex_security.html#apexdangerousmethods — "Checks against calling dangerous methods"; on `Configuration.disableTriggerCRUDSecurity()`: "Disabling CRUD security opens the door to several attacks and requires manual validation, which is unreliable."
 https://github.com/apex-enterprise-patterns/fflib-apex-common/blob/master/sfdx-source/apex-common/main/classes/fflib_SObjectDomain.cls — `Configuration.EnforcingTriggerCRUDSecurity` is documented as "True if the base class is checking the users CRUD requirements before invoking trigger methods"; `handleAfterInsert()` throws `DomainException('Permission to create an ' + name + ' denied.')` when it is on and `SObjectDescribe.isCreateable()` is false. It is a library check, not a platform setting.
-AGENTS.md, "Change Management — Locked Decisions Protocol": why a detail of a standard object cannot be granted by a 2GP permission set, so its field permissions are inert and `isCreateable()` is false for every non-admin user.</t>
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -709,14 +709,14 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Both call sites are annotated in place. In `RecurringDonations` the call sits behind an explicit `suppressTriggerCrudCheck` flag rather than being unconditional. The wider reasoning—that field permissions are inert without object access on a master-detail detail object—is written up in the Change Management section of AGENTS.md and in the `EventTicketTypesSelector` class header.</t>
+          <t>Both call sites are annotated in place. In `RecurringDonations` the call sits behind an explicit `suppressTriggerCrudCheck` flag rather than being unconditional. The wider reasoning—that field permissions are inert without object access on a master-detail detail object—is written in the `EventTicketTypesSelector` class header, which ships in the package: a detail of a standard object cannot be granted by a packaged permission set (Salesforce ignores standard-object permissions at install, cited below), so its field permissions are inert and `isCreateable()` is false for every user without Modify All Data.</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>https://docs.pmd-code.org/pmd-doc-7.26.0/pmd_rules_apex_security.html#apexdangerousmethods — "Checks against calling dangerous methods"; on `Configuration.disableTriggerCRUDSecurity()`: "Disabling CRUD security opens the door to several attacks and requires manual validation, which is unreliable."
 https://github.com/apex-enterprise-patterns/fflib-apex-common/blob/master/sfdx-source/apex-common/main/classes/fflib_SObjectDomain.cls — `Configuration.EnforcingTriggerCRUDSecurity` is documented as "True if the base class is checking the users CRUD requirements before invoking trigger methods"; `handleAfterInsert()` throws `DomainException('Permission to create an ' + name + ' denied.')` when it is on and `SObjectDescribe.isCreateable()` is false. It is a library check, not a platform setting.
-AGENTS.md, "Change Management — Locked Decisions Protocol": why a detail of a standard object cannot be granted by a 2GP permission set, so its field permissions are inert and `isCreateable()` is false for every non-admin user.</t>
+https://developer.salesforce.com/docs/atlas.en-us.pkg2_dev.meta/pkg2_dev/packaging_permission_set_groups.htm — "You can't include object permissions for standard objects in managed packages. During package installation, all object permissions for standard objects are ignored, and aren't installed in the org." Confirmed for this package on 2026-08-16: the installed permission set, retrieved from a subscriber org, carried none of the standard-object grants present in the source XML.</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the only credential-related field in the package, `Payment_Account__c.Stripe_Donor_Restricted_Key__c`, holds the API name of a Named Credential the subscriber administrator creates in Setup and is consumed as `'callout:' + name`, which is what the rule's remediation is for.</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the only credential-related field in the package, `Payment_Account__c.Stripe_Donor_Restricted_Key__c`, holds the API name of a Named Credential the subscriber administrator creates in Setup and is consumed as `'callout:' + name`, which is what the rule's remediation is for.</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>The claim that this value should be stored in a protected custom setting is false because it is not an org-wide secret and no setting could hold it: it is a per-record capability token minted server-side for one guest checkout. It is a 256-bit random value (`SecureTokens.opaque()`, 64 hex characters) written to a unique external-Id field on the staging row, scopes three guest actions to that single row, cannot address any other record, and dies with the row when the checkout completes or the staging retention job purges it. Its entropy, expiry, single-use, revocation and guest-FLS properties are written in the field's `&lt;description&gt;` and tabulated in FP-16 of the readiness document. Holding it in a protected setting would make it org-wide, which is the opposite of the control it provides.</t>
+          <t>The claim that this value should be stored in a protected custom setting is false because it is not an org-wide secret and no setting could hold it: it is a per-record capability token minted server-side for one guest checkout. It is a 256-bit random value (`SecureTokens.opaque()`, 64 hex characters) written to a unique external-Id field on the staging row, scopes three guest actions to that single row, cannot address any other record, and dies with the row when the checkout completes or the staging retention job purges it. Its properties are written in the field's `&lt;description&gt;`: 256-bit entropy, a life bounded by the staging row (terminal at finalize, purged by the retention job), a scope of three actions on that row, revocation with the row, and no guest field access. Holding it in a protected setting would make it org-wide, which is the opposite of the control it provides.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>256-bit random capability token scoped to one staging row; properties in FP-16.</t>
+          <t>256-bit random capability token scoped to one staging row; properties in the field description.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+          <t>The five properties of each token are written in the field `&lt;description&gt;`. `Opportunity.Receipt_Token__c`: 128-bit (`Crypto.generateAesKey(128)`, hex), no expiry by design because a receipt is a permanent read-only record that can act on nothing, reusable, revoked by regenerating the field, no guest field access. `Donation_Staging__c.Access_Token__c`: 256-bit (`SecureTokens.opaque(32)`, 64 hex characters), lives as long as the staging row (terminal status at finalize, purged by the retention job after `Data_Retention_Days__c`, default 90), scoped to three actions on that one row, revoked with the row, no guest field access. The portal access code: 40-bit Crockford-base32, stored only as a SHA-256 hash, single-use (the hash is nulled at redemption and five wrong attempts lock the row), never placed in a URL. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -926,8 +926,7 @@
           <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." A protected setting is org-wide configuration; these fields are per-record transaction state, so the remediation cannot apply.
 https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — protected custom settings and protected custom metadata are the module's stores for "API keys or other secret keys"; a per-checkout nonce or a hash of a one-time code is neither.
 https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
-base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.
-docs/security/appexchange-security-review-readiness.md, FP-16 — the token table: entropy, expiry, single-use, revocation and guest-FLS posture for every URL-borne token.</t>
+base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.</t>
         </is>
       </c>
     </row>
@@ -989,7 +988,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+          <t>The five properties of each token are written in the field `&lt;description&gt;`. `Opportunity.Receipt_Token__c`: 128-bit (`Crypto.generateAesKey(128)`, hex), no expiry by design because a receipt is a permanent read-only record that can act on nothing, reusable, revoked by regenerating the field, no guest field access. `Donation_Staging__c.Access_Token__c`: 256-bit (`SecureTokens.opaque(32)`, 64 hex characters), lives as long as the staging row (terminal status at finalize, purged by the retention job after `Data_Retention_Days__c`, default 90), scoped to three actions on that one row, revoked with the row, no guest field access. The portal access code: 40-bit Crockford-base32, stored only as a SHA-256 hash, single-use (the hash is nulled at redemption and five wrong attempts lock the row), never placed in a URL. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -997,8 +996,7 @@
           <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." A protected setting is org-wide configuration; these fields are per-record transaction state, so the remediation cannot apply.
 https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — protected custom settings and protected custom metadata are the module's stores for "API keys or other secret keys"; a per-checkout nonce or a hash of a one-time code is neither.
 https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
-base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.
-docs/security/appexchange-security-review-readiness.md, FP-16 — the token table: entropy, expiry, single-use, revocation and guest-FLS posture for every URL-borne token.</t>
+base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1058,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+          <t>The five properties of each token are written in the field `&lt;description&gt;`. `Opportunity.Receipt_Token__c`: 128-bit (`Crypto.generateAesKey(128)`, hex), no expiry by design because a receipt is a permanent read-only record that can act on nothing, reusable, revoked by regenerating the field, no guest field access. `Donation_Staging__c.Access_Token__c`: 256-bit (`SecureTokens.opaque(32)`, 64 hex characters), lives as long as the staging row (terminal status at finalize, purged by the retention job after `Data_Retention_Days__c`, default 90), scoped to three actions on that one row, revoked with the row, no guest field access. The portal access code: 40-bit Crockford-base32, stored only as a SHA-256 hash, single-use (the hash is nulled at redemption and five wrong attempts lock the row), never placed in a URL. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1068,8 +1066,7 @@
           <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." A protected setting is org-wide configuration; these fields are per-record transaction state, so the remediation cannot apply.
 https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — protected custom settings and protected custom metadata are the module's stores for "API keys or other secret keys"; a per-checkout nonce or a hash of a one-time code is neither.
 https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
-base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.
-docs/security/appexchange-security-review-readiness.md, FP-16 — the token table: entropy, expiry, single-use, revocation and guest-FLS posture for every URL-borne token.</t>
+base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1128,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. AGENTS.md Rule 9 makes this the required pattern, and FP-4 in docs/security/appexchange-security-review-readiness.md documents it for the reviewer.</t>
+          <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. The package ships no Named Credential and stores no key in any field, setting, metadata record, static resource or Apex literal: the subscriber administrator creates the credential in Setup and the field records only its API name.</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1139,8 +1136,7 @@
           <t>https://docs.stripe.com/keys — the publishable key (`pk_…`) is "Safe to expose: Yes … It can identify your account and create tokens or PaymentMethods from payment details, but it can't perform sensitive operations such as creating charges or reading account data. You can include it in front-end code"; restricted and secret keys are not safe to expose and "Don't put keys in source code or configuration files."
 https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — Named Credentials are "a mechanism for securely managing authentication values for external providers and services"; the module's remediation for an API key is a Named Credential or a protected setting, which is exactly where the key lives here.
 https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_callouts_named_credentials.htm — Apex callouts through Named Credentials (`callout:&lt;name&gt;`), the construction `StripeGateway.cls` uses (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
-base/main/default/classes/payment/gateway/StripeGateway.cls — `this.donorEndpoint = 'callout:' + acct.Stripe_Donor_Restricted_Key__c;` and the matching admin line: the field value is a Named Credential name.
-docs/security/appexchange-security-review-readiness.md, FP-4 — the Named-Credentials-only rule and the reviewer-facing write-up.</t>
+base/main/default/classes/payment/gateway/StripeGateway.cls — `this.donorEndpoint = 'callout:' + acct.Stripe_Donor_Restricted_Key__c;` and the matching admin line: the field value is a Named Credential name.</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. AGENTS.md Rule 9 makes this the required pattern, and FP-4 in docs/security/appexchange-security-review-readiness.md documents it for the reviewer.</t>
+          <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. The package ships no Named Credential and stores no key in any field, setting, metadata record, static resource or Apex literal: the subscriber administrator creates the credential in Setup and the field records only its API name.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1210,8 +1206,7 @@
           <t>https://docs.stripe.com/keys — the publishable key (`pk_…`) is "Safe to expose: Yes … It can identify your account and create tokens or PaymentMethods from payment details, but it can't perform sensitive operations such as creating charges or reading account data. You can include it in front-end code"; restricted and secret keys are not safe to expose and "Don't put keys in source code or configuration files."
 https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — Named Credentials are "a mechanism for securely managing authentication values for external providers and services"; the module's remediation for an API key is a Named Credential or a protected setting, which is exactly where the key lives here.
 https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_callouts_named_credentials.htm — Apex callouts through Named Credentials (`callout:&lt;name&gt;`), the construction `StripeGateway.cls` uses (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
-base/main/default/classes/payment/gateway/StripeGateway.cls — `this.donorEndpoint = 'callout:' + acct.Stripe_Donor_Restricted_Key__c;` and the matching admin line: the field value is a Named Credential name.
-docs/security/appexchange-security-review-readiness.md, FP-4 — the Named-Credentials-only rule and the reviewer-facing write-up.</t>
+base/main/default/classes/payment/gateway/StripeGateway.cls — `this.donorEndpoint = 'callout:' + acct.Stripe_Donor_Restricted_Key__c;` and the matching admin line: the field value is a Named Credential name.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1268,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. AGENTS.md Rule 9 makes this the required pattern, and FP-4 in docs/security/appexchange-security-review-readiness.md documents it for the reviewer.</t>
+          <t>Both restricted-key fields say in their `&lt;description&gt;` that they hold a name and that an unrestricted secret key is not an acceptable value for the credential behind it; `StripeGateway.cls` builds the endpoint as `'callout:' + acct.Stripe_Donor_Restricted_Key__c`. The package ships no Named Credential and stores no key in any field, setting, metadata record, static resource or Apex literal: the subscriber administrator creates the credential in Setup and the field records only its API name.</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1281,8 +1276,7 @@
           <t>https://docs.stripe.com/keys — the publishable key (`pk_…`) is "Safe to expose: Yes … It can identify your account and create tokens or PaymentMethods from payment details, but it can't perform sensitive operations such as creating charges or reading account data. You can include it in front-end code"; restricted and secret keys are not safe to expose and "Don't put keys in source code or configuration files."
 https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — Named Credentials are "a mechanism for securely managing authentication values for external providers and services"; the module's remediation for an API key is a Named Credential or a protected setting, which is exactly where the key lives here.
 https://developer.salesforce.com/docs/atlas.en-us.apexcode.meta/apexcode/apex_callouts_named_credentials.htm — Apex callouts through Named Credentials (`callout:&lt;name&gt;`), the construction `StripeGateway.cls` uses (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
-base/main/default/classes/payment/gateway/StripeGateway.cls — `this.donorEndpoint = 'callout:' + acct.Stripe_Donor_Restricted_Key__c;` and the matching admin line: the field value is a Named Credential name.
-docs/security/appexchange-security-review-readiness.md, FP-4 — the Named-Credentials-only rule and the reviewer-facing write-up.</t>
+base/main/default/classes/payment/gateway/StripeGateway.cls — `this.donorEndpoint = 'callout:' + acct.Stripe_Donor_Restricted_Key__c;` and the matching admin line: the field value is a Named Credential name.</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1338,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+          <t>The five properties of each token are written in the field `&lt;description&gt;`. `Opportunity.Receipt_Token__c`: 128-bit (`Crypto.generateAesKey(128)`, hex), no expiry by design because a receipt is a permanent read-only record that can act on nothing, reusable, revoked by regenerating the field, no guest field access. `Donation_Staging__c.Access_Token__c`: 256-bit (`SecureTokens.opaque(32)`, 64 hex characters), lives as long as the staging row (terminal status at finalize, purged by the retention job after `Data_Retention_Days__c`, default 90), scoped to three actions on that one row, revoked with the row, no guest field access. The portal access code: 40-bit Crockford-base32, stored only as a SHA-256 hash, single-use (the hash is nulled at redemption and five wrong attempts lock the row), never placed in a URL. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1352,8 +1346,7 @@
           <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." A protected setting is org-wide configuration; these fields are per-record transaction state, so the remediation cannot apply.
 https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — protected custom settings and protected custom metadata are the module's stores for "API keys or other secret keys"; a per-checkout nonce or a hash of a one-time code is neither.
 https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
-base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.
-docs/security/appexchange-security-review-readiness.md, FP-16 — the token table: entropy, expiry, single-use, revocation and guest-FLS posture for every URL-borne token.</t>
+base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1408,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>The five properties of each URL-borne token (entropy, expiry, single-use, revocation, guest FLS posture) are written in the field `&lt;description&gt;` and tabulated in FP-16 of docs/security/appexchange-security-review-readiness.md. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
+          <t>The five properties of each token are written in the field `&lt;description&gt;`. `Opportunity.Receipt_Token__c`: 128-bit (`Crypto.generateAesKey(128)`, hex), no expiry by design because a receipt is a permanent read-only record that can act on nothing, reusable, revoked by regenerating the field, no guest field access. `Donation_Staging__c.Access_Token__c`: 256-bit (`SecureTokens.opaque(32)`, 64 hex characters), lives as long as the staging row (terminal status at finalize, purged by the retention job after `Data_Retention_Days__c`, default 90), scoped to three actions on that one row, revoked with the row, no guest field access. The portal access code: 40-bit Crockford-base32, stored only as a SHA-256 hash, single-use (the hash is nulled at redemption and five wrong attempts lock the row), never placed in a URL. `SecureTokens.opaque()` mints the staging token; `DonorPortalService` writes only hashes to `Portal_Access_Token__c`.</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1423,8 +1416,7 @@
           <t>Code Analyzer's own rule definition (AppExchange_xml.xml inside the bundled sfca-pmd-rules jar): the rule message is "To store secrets, use Protected Custom settings or Protected Custom metadata." A protected setting is org-wide configuration; these fields are per-record transaction state, so the remediation cannot apply.
 https://trailhead.salesforce.com/content/learn/modules/secure-secrets-storage/protect-secrets-using-platform-features — protected custom settings and protected custom metadata are the module's stores for "API keys or other secret keys"; a per-checkout nonce or a hash of a one-time code is neither.
 https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#protectsensitivedata — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
-base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.
-docs/security/appexchange-security-review-readiness.md, FP-16 — the token table: entropy, expiry, single-use, revocation and guest-FLS posture for every URL-borne token.</t>
+base/main/default/classes/donor/service/DonorPortalService.cls — `Code_Hash__c = hashToken(rawCode)` on issue, `Code_Hash__c = null` on redemption ("single-use: replay fails structurally"), `Session_Hash__c = hashToken(sessionToken)`; the raw values are never written.</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1478,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the only credential-related field in the package, `Payment_Account__c.Stripe_Donor_Restricted_Key__c`, holds the API name of a Named Credential the subscriber administrator creates in Setup and is consumed as `'callout:' + name`, which is what the rule's remediation is for.</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1556,7 +1548,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the only credential-related field in the package, `Payment_Account__c.Stripe_Donor_Restricted_Key__c`, holds the API name of a Named Credential the subscriber administrator creates in Setup and is consumed as `'callout:' + name`, which is what the rule's remediation is for.</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1626,7 +1618,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the only credential-related field in the package, `Payment_Account__c.Stripe_Donor_Restricted_Key__c`, holds the API name of a Named Credential the subscriber administrator creates in Setup and is consumed as `'callout:' + name`, which is what the rule's remediation is for.</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1696,7 +1688,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the only credential-related field in the package, `Payment_Account__c.Stripe_Donor_Restricted_Key__c`, holds the API name of a Named Credential the subscriber administrator creates in Setup and is consumed as `'callout:' + name`, which is what the rule's remediation is for.</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1766,7 +1758,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the only credential-related field in the package, `Payment_Account__c.Stripe_Donor_Restricted_Key__c`, holds the API name of a Named Credential the subscriber administrator creates in Setup and is consumed as `'callout:' + name`, which is what the rule's remediation is for.</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1836,7 +1828,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the only credential-related field in the package, `Payment_Account__c.Stripe_Donor_Restricted_Key__c`, holds the API name of a Named Credential the subscriber administrator creates in Setup and is consumed as `'callout:' + name`, which is what the rule's remediation is for.</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1906,7 +1898,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the only credential-related field in the package, `Payment_Account__c.Stripe_Donor_Restricted_Key__c`, holds the API name of a Named Credential the subscriber administrator creates in Setup and is consumed as `'callout:' + name`, which is what the rule's remediation is for.</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1976,7 +1968,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the org-wide credentials live only in Named Credentials (FP-4 in docs/security/appexchange-security-review-readiness.md), which is what the rule's remediation is for.</t>
+          <t>Each field's `&lt;description&gt;` in base/main/default/objects/ says what it holds. The package stores no secret in any Custom Setting, protected or not — the only credential-related field in the package, `Payment_Account__c.Stripe_Donor_Restricted_Key__c`, holds the API name of a Named Credential the subscriber administrator creates in Setup and is consumed as `'callout:' + name`, which is what the rule's remediation is for.</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2046,15 +2038,14 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>`grep -rn 'loadScript\|loadStyle' base/main/default/lwc` returns nothing, and these two pages are the only `&lt;script src=` in the package. `js.stripe.com` is a packaged CSP trusted site. The exception is written up as FP-9 in docs/security/appexchange-security-review-readiness.md, and the pages carry the reason in a comment beside the tag.</t>
+          <t>`grep -rn 'loadScript\|loadStyle' base/main/default/lwc` returns nothing, and these two pages are the only `&lt;script src=` in the package. `js.stripe.com` is a packaged CSP trusted site. Both pages carry the reason in a comment beside the tag: Stripe's host keeps the integration in PCI SAQ-A scope, `/v3/` is Stripe's supported evergreen version, and `js.stripe.com` is declared to the platform as a packaged CSP trusted site.</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>https://docs.stripe.com/js/including — "Include the Stripe.js script on each page of your site—it should always be loaded directly from https://js.stripe.com, rather than included in a bundle or hosted yourself."
 https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#loadjavascripthtmlscript — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
-base/main/default/cspTrustedSites/Stripe_js.cspTrustedSite-meta.xml — `js.stripe.com` is a packaged CSP trusted site, so the load is declared to the platform rather than slipped past it.
-docs/security/appexchange-security-review-readiness.md, FP-9 — the standing exception and its PCI reasoning.</t>
+base/main/default/cspTrustedSites/Stripe_js.cspTrustedSite-meta.xml — `js.stripe.com` is a packaged CSP trusted site, so the load is declared to the platform rather than slipped past it.</t>
         </is>
       </c>
     </row>
@@ -2116,15 +2107,14 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>`grep -rn 'loadScript\|loadStyle' base/main/default/lwc` returns nothing, and these two pages are the only `&lt;script src=` in the package. `js.stripe.com` is a packaged CSP trusted site. The exception is written up as FP-9 in docs/security/appexchange-security-review-readiness.md, and the pages carry the reason in a comment beside the tag.</t>
+          <t>`grep -rn 'loadScript\|loadStyle' base/main/default/lwc` returns nothing, and these two pages are the only `&lt;script src=` in the package. `js.stripe.com` is a packaged CSP trusted site. Both pages carry the reason in a comment beside the tag: Stripe's host keeps the integration in PCI SAQ-A scope, `/v3/` is Stripe's supported evergreen version, and `js.stripe.com` is declared to the platform as a packaged CSP trusted site.</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
           <t>https://docs.stripe.com/js/including — "Include the Stripe.js script on each page of your site—it should always be loaded directly from https://js.stripe.com, rather than included in a bundle or hosted yourself."
 https://developer.salesforce.com/docs/platform/salesforce-code-analyzer/guide/rules-pmd-appexchange.html#loadjavascripthtmlscript — the scanner's reference for this rule (page could not be retrieved while this document was prepared: the host answers automated requests with HTTP 403, so it is cited as the scanner's own reference link and not quoted).
-base/main/default/cspTrustedSites/Stripe_js.cspTrustedSite-meta.xml — `js.stripe.com` is a packaged CSP trusted site, so the load is declared to the platform rather than slipped past it.
-docs/security/appexchange-security-review-readiness.md, FP-9 — the standing exception and its PCI reasoning.</t>
+base/main/default/cspTrustedSites/Stripe_js.cspTrustedSite-meta.xml — `js.stripe.com` is a packaged CSP trusted site, so the load is declared to the platform rather than slipped past it.</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2201,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>36949d12</t>
+          <t>a4b2d3f1</t>
         </is>
       </c>
     </row>
